--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26中信银行三农债BC</t>
+          <t>26中信银行三农债01BC</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -700,7 +700,11 @@
           <t>10-22 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>212680077.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -709,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>100.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>100.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.90</t>
@@ -739,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -924,7 +930,11 @@
           <t>10-22 17:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>212680081.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -933,7 +943,9 @@
       <c r="E4" s="4" t="n">
         <v>75.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>75.0</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -959,7 +971,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5100</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -999,7 +1011,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.60%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>

--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 81.79</t>
+          <t>A+ 82.81</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -872,21 +872,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>股份制银行</t>
-        </is>
-      </c>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
       <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -947,8 +935,12 @@
         <v>75.0</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>28.33</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -971,7 +963,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5100</t>
+          <t>1.5450/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -981,7 +973,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A 77.77</t>
+          <t>A 79.38</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1090,21 +1082,9 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>股份制银行</t>
-        </is>
-      </c>
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
       <c r="AT4" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -1148,7 +1128,11 @@
           <t>10-22 16:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>212680074.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1157,14 +1141,20 @@
       <c r="E5" s="4" t="n">
         <v>15.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>34.33</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -1197,7 +1187,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 40.75</t>
+          <t>B- 44.18</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1220,7 +1210,9 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>2.68</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1314,21 +1306,9 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
+      <c r="AQ5" s="3"/>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="3"/>
       <c r="AT5" s="3" t="inlineStr">
         <is>
           <t>银行</t>

--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -872,9 +872,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -1082,9 +1094,21 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="AQ4" s="3"/>
-      <c r="AR4" s="3"/>
-      <c r="AS4" s="3"/>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -1306,9 +1330,21 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="3"/>
-      <c r="AS5" s="3"/>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
           <t>银行</t>

--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-26" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-23</t>
+          <t>数据来源：DM    2026-10-26</t>
         </is>
       </c>
     </row>
@@ -721,8 +721,12 @@
           <t>1.30 ~ 1.90</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>25.33</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -755,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 82.81</t>
+          <t>S- 85.59</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -922,17 +926,17 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债02</t>
+          <t>26重庆三峡银行债02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-22 17:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>212680081.IB</t>
+          <t>212680074.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -941,51 +945,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.0</v>
+        <v>15.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>28.33</v>
+        <v>34.33</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债01</t>
+          <t>26重庆三峡银行债01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.6085</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.5450/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A 79.38</t>
+          <t>B- 42.75</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -995,7 +1003,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:30</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1005,19 +1013,21 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>2.68</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.60%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1025,18 +1035,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC4" s="3"/>
+          <t>本期债券的募集资金将优先用于“西部陆海新通道”项下贷款，依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,西南证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
@@ -1045,7 +1063,7 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
@@ -1055,7 +1073,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
+          <t>重庆三峡银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1065,7 +1083,7 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2029-10-26</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1076,12 +1094,12 @@
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
@@ -1091,7 +1109,7 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1106,7 +1124,7 @@
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
@@ -1144,17 +1162,17 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债02</t>
+          <t>26浙商银行债02</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>10-22 16:00</t>
+          <t>10-22 17:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>212680074.IB</t>
+          <t>212680081.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1163,55 +1181,51 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>15.0</v>
+        <v>75.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
+        <v>75.0</v>
+      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="4" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>34.33</v>
+        <v>28.33</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债01</t>
+          <t>26浙商银行债01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.6085</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5450/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 44.18</t>
+          <t>A 73.65</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1221,7 +1235,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 09:30</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1231,21 +1245,19 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>2.68</v>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.50%~1.60%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1253,26 +1265,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将优先用于“西部陆海新通道”项下贷款，依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,西南证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
@@ -1281,7 +1285,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
@@ -1291,7 +1295,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年金融债券(第二期)</t>
+          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1301,23 +1305,23 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2029-10-26</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
@@ -1327,7 +1331,7 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -926,17 +926,17 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债02</t>
+          <t>26浙商银行债02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-22 16:00</t>
+          <t>10-22 17:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>212680074.IB</t>
+          <t>212680081.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -945,55 +945,51 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>15.0</v>
+        <v>75.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
+        <v>75.0</v>
+      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="4" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>34.33</v>
+        <v>28.33</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债01</t>
+          <t>26浙商银行债01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.6085</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5450/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 42.75</t>
+          <t>A 73.65</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 09:30</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1013,21 +1009,19 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>2.68</v>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.50%~1.60%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1035,26 +1029,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将优先用于“西部陆海新通道”项下贷款，依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,西南证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1049,7 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
@@ -1073,7 +1059,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年金融债券(第二期)</t>
+          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1083,23 +1069,23 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-10-26</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
@@ -1109,7 +1095,7 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1124,7 +1110,7 @@
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
@@ -1162,17 +1148,17 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债02</t>
+          <t>26重庆三峡银行债02</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>10-22 17:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>212680081.IB</t>
+          <t>212680074.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1181,51 +1167,55 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>75.0</v>
+        <v>15.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="G5" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>28.33</v>
+        <v>34.33</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债01</t>
+          <t>26重庆三峡银行债01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.6085</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.5450/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>A 73.65</t>
+          <t>B- 42.75</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1235,7 +1225,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:30</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1245,19 +1235,21 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="U5" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>2.68</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.60%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1265,18 +1257,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC5" s="3"/>
+          <t>本期债券的募集资金将优先用于“西部陆海新通道”项下贷款，依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,西南证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
+          <t>重庆三峡银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1305,25 +1305,25 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2029-10-26</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-26" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-27" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-26</t>
+          <t>数据来源：DM    2026-10-27</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>S- 85.59</t>
+          <t>A+ 84.71</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -853,7 +853,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A 73.65</t>
+          <t>A 75.66</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 42.75</t>
+          <t>B- 39.53</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1311,7 +1311,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-22.xlsx
+++ b/data/credit_bond_2026-10-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-27</t>
+          <t>数据来源：DM    2026-10-28</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 84.71</t>
+          <t>S- 87.90</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -926,17 +926,17 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债02</t>
+          <t>26重庆三峡银行债02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-22 17:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>212680081.IB</t>
+          <t>212680074.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -945,51 +945,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.0</v>
+        <v>15.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>28.33</v>
+        <v>34.33</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债01</t>
+          <t>26重庆三峡银行债01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>1.6085</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.5450/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A 75.66</t>
+          <t>B- 48.62</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:30</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1009,19 +1013,21 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>2.68</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.60%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1029,18 +1035,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC4" s="3"/>
+          <t>本期债券的募集资金将优先用于“西部陆海新通道”项下贷款，依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,西南证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
@@ -1049,7 +1063,7 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
@@ -1059,7 +1073,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
+          <t>重庆三峡银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1069,25 +1083,25 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2029-10-26</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1110,7 +1124,7 @@
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
@@ -1148,17 +1162,17 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债02</t>
+          <t>26浙商银行债02</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>10-22 16:00</t>
+          <t>10-22 17:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>212680074.IB</t>
+          <t>212680081.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1167,55 +1181,51 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>15.0</v>
+        <v>75.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
+        <v>75.0</v>
+      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="4" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>34.33</v>
+        <v>28.33</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债01</t>
+          <t>26浙商银行债01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.6085</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5450/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 39.53</t>
+          <t>A 76.63</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1225,7 +1235,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 09:30</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1235,21 +1245,19 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>2.68</v>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.50%~1.60%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1257,26 +1265,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将优先用于“西部陆海新通道”项下贷款，依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,西南证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,华夏银行股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年金融债券(第二期)</t>
+          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2029-10-26</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
